--- a/data/trans_bre/P57GLOBAL_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P57GLOBAL_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 4,83</t>
+          <t>-3,83; 4,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 12,55</t>
+          <t>2,74; 12,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 9,73</t>
+          <t>0,91; 9,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 9,52</t>
+          <t>-0,95; 9,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 6,45</t>
+          <t>-4,82; 6,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 20,32</t>
+          <t>4,16; 20,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 12,67</t>
+          <t>1,26; 12,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 17,26</t>
+          <t>-1,52; 16,8</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 8,04</t>
+          <t>-0,47; 7,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 10,29</t>
+          <t>1,69; 10,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 8,62</t>
+          <t>1,91; 8,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 38,94</t>
+          <t>1,6; 40,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 11,68</t>
+          <t>-0,65; 11,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 15,54</t>
+          <t>2,37; 15,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 10,73</t>
+          <t>2,27; 10,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 133,58</t>
+          <t>2,43; 149,44</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 8,06</t>
+          <t>-2,14; 8,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 9,05</t>
+          <t>-0,87; 9,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,18</t>
+          <t>-3,66; 3,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 1,86</t>
+          <t>-13,41; 3,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 12,74</t>
+          <t>-3,26; 13,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 14,23</t>
+          <t>-1,27; 14,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 3,74</t>
+          <t>-4,17; 4,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 2,82</t>
+          <t>-19,59; 4,66</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 4,32</t>
+          <t>-3,56; 4,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 11,04</t>
+          <t>3,7; 11,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 5,02</t>
+          <t>-1,7; 4,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 2,05</t>
+          <t>-15,2; 1,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 6,34</t>
+          <t>-4,93; 6,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 15,31</t>
+          <t>4,89; 15,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 6,41</t>
+          <t>-2,08; 6,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 3,33</t>
+          <t>-24,94; 3,05</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,04</t>
+          <t>-0,39; 3,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,72</t>
+          <t>4,09; 8,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,7</t>
+          <t>1,02; 4,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 17,97</t>
+          <t>-1,83; 17,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,87</t>
+          <t>-0,54; 5,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,92</t>
+          <t>5,84; 12,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,86</t>
+          <t>1,22; 6,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 39,57</t>
+          <t>-3,05; 36,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57GLOBAL_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P57GLOBAL_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,75</t>
+          <t>-4,08; 4,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 12,51</t>
+          <t>2,45; 12,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,37</t>
+          <t>1,6; 9,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 9,21</t>
+          <t>-2,39; 8,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 6,32</t>
+          <t>-5,18; 6,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 20,33</t>
+          <t>3,88; 20,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 12,1</t>
+          <t>1,91; 12,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 16,8</t>
+          <t>-3,7; 15,44</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,42</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 7,89</t>
+          <t>-0,31; 7,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 10,07</t>
+          <t>1,69; 10,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 8,47</t>
+          <t>1,68; 8,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 40,94</t>
+          <t>-1,52; 7,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 11,64</t>
+          <t>-0,43; 11,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 15,19</t>
+          <t>2,37; 15,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,62</t>
+          <t>2,01; 10,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 149,44</t>
+          <t>-2,21; 11,62</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,81</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-5,75%</t>
+          <t>-2,57%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 8,38</t>
+          <t>-2,4; 8,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 9,15</t>
+          <t>-0,95; 8,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 3,57</t>
+          <t>-4,05; 3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 3,0</t>
+          <t>-6,67; 3,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 13,87</t>
+          <t>-3,56; 12,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 14,79</t>
+          <t>-1,3; 13,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,25</t>
+          <t>-4,59; 3,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 4,66</t>
+          <t>-9,39; 5,43</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,81</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-6,16%</t>
+          <t>-0,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 4,54</t>
+          <t>-3,32; 4,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 11,31</t>
+          <t>3,52; 11,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,92</t>
+          <t>-1,81; 4,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 1,85</t>
+          <t>-4,63; 4,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 6,77</t>
+          <t>-4,56; 7,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 15,82</t>
+          <t>4,71; 15,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 6,25</t>
+          <t>-2,17; 6,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 3,05</t>
+          <t>-6,98; 6,88</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,91</t>
+          <t>-0,48; 4,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,57</t>
+          <t>4,12; 8,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,86</t>
+          <t>1,06; 4,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 17,47</t>
+          <t>-1,33; 3,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,68</t>
+          <t>-0,68; 5,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,8</t>
+          <t>5,89; 12,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,0</t>
+          <t>1,28; 5,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 36,75</t>
+          <t>-2,02; 5,56</t>
         </is>
       </c>
     </row>
